--- a/卡牌设计数据库.xlsx
+++ b/卡牌设计数据库.xlsx
@@ -1332,263 +1332,263 @@
         <is>
           <t>消耗，魔法书。
 给予自身1层虚弱，给予所有敌人1层虚弱。
+获得6点格挡。
+解读：抽1张牌。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>额外给予所有敌人1层虚弱，增加3点格挡。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>消耗, 魔法书牌, 解读</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>「翡翠的排挤原理」</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>小恶魔</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>衍生</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>消耗，保留，魔法书。
+给予自身1层虚弱、1层易伤，给予所有敌人2层虚弱、2层易伤。
+获得11点格挡。
+解读：抽1张牌。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>额外给予所有敌人1层虚弱和1层易伤，增加3点格挡。</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>消耗, 魔法书牌, 解读, 保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>「红宝石之书」</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>小恶魔</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>衍生</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>消耗，魔法书。
+获得1点临时敏捷和1点临时力量。
+获得5点格挡。
+解读：抽1张牌。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>增加1点临时力量和临时敏捷，增加3点格挡。</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>消耗, 魔法书牌, 解读</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>「红宝石的天作之合」</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>小恶魔</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>衍生</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>消耗，保留，魔法书。
+获得1点敏捷和1点力量。
+获得10点格挡。
+解读：抽1张牌。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>增加1点力量和敏捷，增加3点格挡。</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>消耗, 魔法书牌, 解读, 保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>「蓝宝石之书」</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>小恶魔</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>衍生</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>消耗，魔法书。
+获得蓝宝石的加护。
+获得4点格挡。
+解读：抽1张牌。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>增加3点格挡。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>消耗, 魔法书牌, 解读</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="51" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>「蓝宝石的存在证明」</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>小恶魔</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>衍生</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>消耗，保留，魔法书。
+获得蓝宝石的存在证明。
 获得8点格挡。
 解读：抽1张牌。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>额外给予所有敌人1层虚弱，增加4点格挡。</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>消耗, 魔法书牌, 解读</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>「翡翠的排挤原理」</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>小恶魔</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>衍生</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>消耗，保留，魔法书。
-给予自身1层虚弱、1层易伤，给予所有敌人3层虚弱、3层易伤。
-获得13点格挡。
-解读：抽1张牌。</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>额外给予所有敌人1层虚弱和1层易伤，增加4点格挡。</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>消耗, 魔法书牌, 解读, 保留</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>「红宝石之书」</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>小恶魔</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>衍生</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>消耗，魔法书。
-获得2点临时敏捷和2点临时力量。
-获得6点格挡。
-解读：抽1张牌。</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>增加1点临时力量和临时敏捷，增加4点格挡。</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>消耗, 魔法书牌, 解读</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="51" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>「红宝石的天作之合」</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>小恶魔</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>衍生</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>消耗，保留，魔法书。
-获得2点敏捷和2点力量。
-获得11点格挡。
-解读：抽1张牌。</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>增加1点力量和敏捷，增加4点格挡。</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>消耗, 魔法书牌, 解读, 保留</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="51" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>「蓝宝石之书」</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>小恶魔</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>衍生</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>消耗，魔法书。
-获得蓝宝石的加护。
-获得6点格挡。
-解读：抽1张牌。</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>增加4点格挡。</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>消耗, 魔法书牌, 解读</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="51" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>「蓝宝石的存在证明」</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>小恶魔</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>衍生</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>消耗，保留，魔法书。
-获得蓝宝石的存在证明。
-获得10点格挡。
-解读：抽1张牌。</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>增加4点格挡。</t>
+          <t>增加3点格挡。</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>消耗，魔法书。
-抽2张牌。
+抽1张牌。
 解读：抽1张牌。</t>
         </is>
       </c>
@@ -1827,7 +1827,7 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>消耗，魔法书。
-获得6点魔力。
+获得4点魔力。
 解读：抽1张牌。</t>
         </is>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>消耗，保留，魔法书。
-获得3点魔力。
+获得2点魔力。
 翻倍你的魔力。
 解读：抽1张牌。</t>
         </is>
@@ -2024,7 +2024,7 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>消耗，魔法书。
-获得3点能量。
+获得2点能量。
 解读：抽1张牌。</t>
         </is>
       </c>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>（这张牌不能以普通的方式从「青金石之书」变化为真名形态，只有在通过魔法书收集生成过所有的非真名状态的魔法书后，才能从「青金石之书」变化为解读形态「青金石的幻想图书馆」）
+          <t>（这张牌不能以普通的方式从「青金石之书」变化为真名形态，只有在通过魔法书收集生成过所有的非真名状态的魔法书后，才能从「青金石之书」变化为真名形态「青金石的幻想图书馆」）
 消耗。
 本场战斗中，当魔法书牌加入手牌时，将其变化为真名形态。</t>
         </is>
@@ -3507,7 +3507,7 @@
         <is>
           <t>获得8点格挡。
 进行1次魔法书收集。
-解读：随机生成1个书符牌，附带保留、消耗。</t>
+解读：随机生成1个技能牌，附带保留、消耗。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5792,7 +5792,7 @@
       <c r="G114" t="inlineStr">
         <is>
           <t>每回合开始时，获得3点魔力。
-当你消耗魔力时，对所有敌人施加1层魔力烧灼。</t>
+当你消耗魔力时，对所有敌人施加2层魔力烧灼。</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="4" ht="38.25" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>瓶装文字</t>
+          <t>液态魔法书</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
